--- a/Employee_Attendance_Report.xlsx
+++ b/Employee_Attendance_Report.xlsx
@@ -38,7 +38,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="22"/>
+      <sz val="21"/>
     </font>
     <font>
       <i val="1"/>
@@ -48,25 +48,24 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
+      <color rgb="005F497A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="005F497A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -75,22 +74,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="007030A0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FC"/>
+        <fgColor rgb="00E4DFEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00F3EFFA"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,34 +100,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -223,6 +215,91 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Department Attendance Profile</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <radarChart>
+        <radarStyle val="filled"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Calc'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Calc'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Calc'!$B$2:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </radarChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Avg Attendance Rate by Month</a:t>
             </a:r>
           </a:p>
@@ -296,253 +373,16 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Avg Attendance Rate by Department</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Calc'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Calc'!$A$2:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Calc'!$B$2:$B$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Total Late Days by Employee</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Calc'!H1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Calc'!$G$2:$G$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Calc'!$H$2:$H$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Avg Attendance Rate by Employee</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Calc'!K1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Calc'!$J$2:$J$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Calc'!$K$2:$K$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4680000" cy="2880000"/>
+    <ext cx="4320000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -561,10 +401,10 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4680000" cy="2880000"/>
+    <ext cx="4320000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -574,50 +414,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4680000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4680000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -912,32 +708,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="2" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EMPLOYEE ATTENDANCE REPORT 2026</t>
+          <t>👥  TEAM ATTENDANCE — MONTHLY SCORECARDS 2026</t>
         </is>
       </c>
     </row>
@@ -945,110 +742,234 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Monthly tracking - attendance rate, late days and absences per employee &amp; department</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>AVG ATTENDANCE RATE</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+          <t>10 employees · 5 departments · 12 months — rates and late days update automatically</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>AVG ATTENDANCE</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>TOTAL LATE DAYS</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>TOTAL ABSENT DAYS</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PERFECT MONTHS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="4">
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="4">
         <f>AVERAGE(Data!H2:H121)</f>
         <v/>
       </c>
-      <c r="E5" s="5">
+      <c r="E6" s="5">
         <f>SUM(Data!E2:E121)</f>
         <v/>
       </c>
-      <c r="H5" s="5">
+      <c r="H6" s="5">
         <f>SUM(Data!F2:F121)</f>
         <v/>
       </c>
-      <c r="K5" s="5">
+      <c r="K6" s="5">
         <f>COUNTIF(Data!H2:H121,1)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>BEST DEPARTMENT</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>TOP EMPLOYEE</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>MOST LATE DAYS</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>BEST MONTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="7">
-        <f>INDEX(Calc!A2:A6,MATCH(MAX(Calc!B2:B6),Calc!B2:B6,0))</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
-        <f>INDEX(Calc!J2:J11,MATCH(MAX(Calc!K2:K11),Calc!K2:K11,0))</f>
-        <v/>
-      </c>
-      <c r="H8" s="7">
-        <f>INDEX(Calc!G2:G11,MATCH(MAX(Calc!H2:H11),Calc!H2:H11,0))</f>
-        <v/>
-      </c>
-      <c r="K8" s="7">
-        <f>INDEX(Calc!D2:D13,MATCH(MAX(Calc!E2:E13),Calc!E2:E13,0))</f>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Carmen Popa</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Georgiana Mara</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Julian Petrescu</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Ana Marinescu</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Filip Barbu</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"Carmen Popa",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+      <c r="E12" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"Georgiana Mara",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+      <c r="H12" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"Julian Petrescu",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+      <c r="K12" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"Ana Marinescu",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+      <c r="N12" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"Filip Barbu",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"Carmen Popa",Data!$E$2:$E$121)&amp;" days"</f>
+        <v/>
+      </c>
+      <c r="E13" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"Georgiana Mara",Data!$E$2:$E$121)&amp;" days"</f>
+        <v/>
+      </c>
+      <c r="H13" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"Julian Petrescu",Data!$E$2:$E$121)&amp;" days"</f>
+        <v/>
+      </c>
+      <c r="K13" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"Ana Marinescu",Data!$E$2:$E$121)&amp;" days"</f>
+        <v/>
+      </c>
+      <c r="N13" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"Filip Barbu",Data!$E$2:$E$121)&amp;" days"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Horia Lazarescu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Bogdan Radu</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Ingrid Marinescu</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>David Stan</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Elena Vasile</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"Horia Lazarescu",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+      <c r="E16" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"Bogdan Radu",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+      <c r="H16" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"Ingrid Marinescu",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+      <c r="K16" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"David Stan",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+      <c r="N16" s="6">
+        <f>AVERAGEIF(Data!$B$2:$B$121,"Elena Vasile",Data!$H$2:$H$121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"Horia Lazarescu",Data!$E$2:$E$121)&amp;" days"</f>
+        <v/>
+      </c>
+      <c r="E17" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"Bogdan Radu",Data!$E$2:$E$121)&amp;" days"</f>
+        <v/>
+      </c>
+      <c r="H17" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"Ingrid Marinescu",Data!$E$2:$E$121)&amp;" days"</f>
+        <v/>
+      </c>
+      <c r="K17" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"David Stan",Data!$E$2:$E$121)&amp;" days"</f>
+        <v/>
+      </c>
+      <c r="N17" s="7">
+        <f>"Late: "&amp;SUMIF(Data!$B$2:$B$121,"Elena Vasile",Data!$E$2:$E$121)&amp;" days"</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="H4:I4"/>
+  <mergeCells count="40">
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="H15:I15"/>
     <mergeCell ref="K5:L5"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="E15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1058,6 +979,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1117,34 +1039,34 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" t="n">
         <v>18</v>
       </c>
-      <c r="E2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="9">
         <f>D2/22</f>
         <v/>
       </c>
@@ -1177,40 +1099,40 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="9">
         <f>D3/22</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" t="n">
         <v>15</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="10">
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="9">
         <f>D4/22</f>
         <v/>
       </c>
@@ -1243,40 +1165,40 @@
       <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="9">
         <f>D5/22</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" t="n">
         <v>16</v>
       </c>
-      <c r="E6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="10">
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9">
         <f>D6/22</f>
         <v/>
       </c>
@@ -1309,40 +1231,40 @@
       <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="9">
         <f>D7/22</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" t="n">
         <v>15</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="10">
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9">
         <f>D8/22</f>
         <v/>
       </c>
@@ -1375,40 +1297,40 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="9">
         <f>D9/22</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="10">
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="9">
         <f>D10/22</f>
         <v/>
       </c>
@@ -1441,40 +1363,40 @@
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="9">
         <f>D11/22</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" t="n">
         <v>18</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="10">
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
         <f>D12/22</f>
         <v/>
       </c>
@@ -1507,40 +1429,40 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="9">
         <f>D13/22</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" t="n">
         <v>19</v>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="10">
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
         <f>D14/22</f>
         <v/>
       </c>
@@ -1573,40 +1495,40 @@
       <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="9">
         <f>D15/22</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" t="n">
         <v>16</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="10">
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
         <f>D16/22</f>
         <v/>
       </c>
@@ -1639,40 +1561,40 @@
       <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="9">
         <f>D17/22</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" t="n">
         <v>17</v>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="10">
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9">
         <f>D18/22</f>
         <v/>
       </c>
@@ -1705,40 +1627,40 @@
       <c r="G19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="9">
         <f>D19/22</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" t="n">
         <v>21</v>
       </c>
-      <c r="E20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="10">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="9">
         <f>D20/22</f>
         <v/>
       </c>
@@ -1771,40 +1693,40 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="9">
         <f>D21/22</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" t="n">
         <v>21</v>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="10">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="9">
         <f>D22/22</f>
         <v/>
       </c>
@@ -1837,40 +1759,40 @@
       <c r="G23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="9">
         <f>D23/22</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" t="n">
         <v>18</v>
       </c>
-      <c r="E24" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="10">
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
         <f>D24/22</f>
         <v/>
       </c>
@@ -1903,40 +1825,40 @@
       <c r="G25" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="9">
         <f>D25/22</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" t="n">
         <v>15</v>
       </c>
-      <c r="E26" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="10">
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="9">
         <f>D26/22</f>
         <v/>
       </c>
@@ -1969,40 +1891,40 @@
       <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="9">
         <f>D27/22</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" t="n">
         <v>15</v>
       </c>
-      <c r="E28" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="10">
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="9">
         <f>D28/22</f>
         <v/>
       </c>
@@ -2035,40 +1957,40 @@
       <c r="G29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="9">
         <f>D29/22</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" t="n">
         <v>17</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="10">
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
         <f>D30/22</f>
         <v/>
       </c>
@@ -2101,40 +2023,40 @@
       <c r="G31" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="9">
         <f>D31/22</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" t="n">
         <v>17</v>
       </c>
-      <c r="E32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="10">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="9">
         <f>D32/22</f>
         <v/>
       </c>
@@ -2167,40 +2089,40 @@
       <c r="G33" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="9">
         <f>D33/22</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" t="n">
         <v>15</v>
       </c>
-      <c r="E34" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="10">
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="9">
         <f>D34/22</f>
         <v/>
       </c>
@@ -2233,40 +2155,40 @@
       <c r="G35" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="9">
         <f>D35/22</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" t="n">
         <v>16</v>
       </c>
-      <c r="E36" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="10">
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="9">
         <f>D36/22</f>
         <v/>
       </c>
@@ -2299,40 +2221,40 @@
       <c r="G37" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="9">
         <f>D37/22</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" t="n">
         <v>17</v>
       </c>
-      <c r="E38" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="10">
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9">
         <f>D38/22</f>
         <v/>
       </c>
@@ -2365,40 +2287,40 @@
       <c r="G39" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39" s="9">
         <f>D39/22</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" t="n">
         <v>16</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" t="n">
         <v>4</v>
       </c>
-      <c r="F40" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="10">
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
         <f>D40/22</f>
         <v/>
       </c>
@@ -2431,40 +2353,40 @@
       <c r="G41" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="9">
         <f>D41/22</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" t="n">
         <v>16</v>
       </c>
-      <c r="E42" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="10">
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="9">
         <f>D42/22</f>
         <v/>
       </c>
@@ -2497,40 +2419,40 @@
       <c r="G43" t="n">
         <v>2</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H43" s="9">
         <f>D43/22</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" t="n">
         <v>20</v>
       </c>
-      <c r="E44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="10">
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="9">
         <f>D44/22</f>
         <v/>
       </c>
@@ -2563,40 +2485,40 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="9">
         <f>D45/22</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" t="n">
         <v>17</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="10">
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="9">
         <f>D46/22</f>
         <v/>
       </c>
@@ -2629,40 +2551,40 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="9">
         <f>D47/22</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D48" s="9" t="n">
+      <c r="D48" t="n">
         <v>22</v>
       </c>
-      <c r="E48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="10">
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
         <f>D48/22</f>
         <v/>
       </c>
@@ -2695,40 +2617,40 @@
       <c r="G49" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="9">
         <f>D49/22</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D50" s="9" t="n">
+      <c r="D50" t="n">
         <v>19</v>
       </c>
-      <c r="E50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="10">
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="9">
         <f>D50/22</f>
         <v/>
       </c>
@@ -2761,40 +2683,40 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="9">
         <f>D51/22</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D52" s="9" t="n">
+      <c r="D52" t="n">
         <v>18</v>
       </c>
-      <c r="E52" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="10">
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
         <f>D52/22</f>
         <v/>
       </c>
@@ -2827,40 +2749,40 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="9">
         <f>D53/22</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D54" s="9" t="n">
+      <c r="D54" t="n">
         <v>21</v>
       </c>
-      <c r="E54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="10">
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
         <f>D54/22</f>
         <v/>
       </c>
@@ -2893,40 +2815,40 @@
       <c r="G55" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="11">
+      <c r="H55" s="9">
         <f>D55/22</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D56" s="9" t="n">
+      <c r="D56" t="n">
         <v>15</v>
       </c>
-      <c r="E56" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" s="10">
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" s="9">
         <f>D56/22</f>
         <v/>
       </c>
@@ -2959,40 +2881,40 @@
       <c r="G57" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="11">
+      <c r="H57" s="9">
         <f>D57/22</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D58" s="9" t="n">
+      <c r="D58" t="n">
         <v>15</v>
       </c>
-      <c r="E58" s="9" t="n">
+      <c r="E58" t="n">
         <v>4</v>
       </c>
-      <c r="F58" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="10">
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="9">
         <f>D58/22</f>
         <v/>
       </c>
@@ -3025,40 +2947,40 @@
       <c r="G59" t="n">
         <v>1</v>
       </c>
-      <c r="H59" s="11">
+      <c r="H59" s="9">
         <f>D59/22</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D60" s="9" t="n">
+      <c r="D60" t="n">
         <v>20</v>
       </c>
-      <c r="E60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="10">
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
         <f>D60/22</f>
         <v/>
       </c>
@@ -3091,40 +3013,40 @@
       <c r="G61" t="n">
         <v>1</v>
       </c>
-      <c r="H61" s="11">
+      <c r="H61" s="9">
         <f>D61/22</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D62" s="9" t="n">
+      <c r="D62" t="n">
         <v>18</v>
       </c>
-      <c r="E62" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="10">
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="9">
         <f>D62/22</f>
         <v/>
       </c>
@@ -3157,40 +3079,40 @@
       <c r="G63" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H63" s="9">
         <f>D63/22</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D64" s="9" t="n">
+      <c r="D64" t="n">
         <v>20</v>
       </c>
-      <c r="E64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" s="10">
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="9">
         <f>D64/22</f>
         <v/>
       </c>
@@ -3223,40 +3145,40 @@
       <c r="G65" t="n">
         <v>1</v>
       </c>
-      <c r="H65" s="11">
+      <c r="H65" s="9">
         <f>D65/22</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D66" s="9" t="n">
+      <c r="D66" t="n">
         <v>15</v>
       </c>
-      <c r="E66" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F66" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G66" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="10">
+      <c r="E66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="9">
         <f>D66/22</f>
         <v/>
       </c>
@@ -3289,40 +3211,40 @@
       <c r="G67" t="n">
         <v>1</v>
       </c>
-      <c r="H67" s="11">
+      <c r="H67" s="9">
         <f>D67/22</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D68" s="9" t="n">
+      <c r="D68" t="n">
         <v>22</v>
       </c>
-      <c r="E68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="10">
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
         <f>D68/22</f>
         <v/>
       </c>
@@ -3355,40 +3277,40 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="11">
+      <c r="H69" s="9">
         <f>D69/22</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D70" s="9" t="n">
+      <c r="D70" t="n">
         <v>18</v>
       </c>
-      <c r="E70" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G70" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="10">
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="9">
         <f>D70/22</f>
         <v/>
       </c>
@@ -3421,40 +3343,40 @@
       <c r="G71" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="11">
+      <c r="H71" s="9">
         <f>D71/22</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D72" s="9" t="n">
+      <c r="D72" t="n">
         <v>14</v>
       </c>
-      <c r="E72" s="9" t="n">
+      <c r="E72" t="n">
         <v>4</v>
       </c>
-      <c r="F72" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="10">
+      <c r="F72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="9">
         <f>D72/22</f>
         <v/>
       </c>
@@ -3487,40 +3409,40 @@
       <c r="G73" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="11">
+      <c r="H73" s="9">
         <f>D73/22</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D74" s="9" t="n">
+      <c r="D74" t="n">
         <v>19</v>
       </c>
-      <c r="E74" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="10">
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
         <f>D74/22</f>
         <v/>
       </c>
@@ -3553,40 +3475,40 @@
       <c r="G75" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="11">
+      <c r="H75" s="9">
         <f>D75/22</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D76" s="9" t="n">
+      <c r="D76" t="n">
         <v>21</v>
       </c>
-      <c r="E76" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="10">
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
         <f>D76/22</f>
         <v/>
       </c>
@@ -3619,40 +3541,40 @@
       <c r="G77" t="n">
         <v>2</v>
       </c>
-      <c r="H77" s="11">
+      <c r="H77" s="9">
         <f>D77/22</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D78" s="9" t="n">
+      <c r="D78" t="n">
         <v>19</v>
       </c>
-      <c r="E78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="10">
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="9">
         <f>D78/22</f>
         <v/>
       </c>
@@ -3685,40 +3607,40 @@
       <c r="G79" t="n">
         <v>0</v>
       </c>
-      <c r="H79" s="11">
+      <c r="H79" s="9">
         <f>D79/22</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D80" s="9" t="n">
+      <c r="D80" t="n">
         <v>15</v>
       </c>
-      <c r="E80" s="9" t="n">
+      <c r="E80" t="n">
         <v>4</v>
       </c>
-      <c r="F80" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="10">
+      <c r="F80" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="9">
         <f>D80/22</f>
         <v/>
       </c>
@@ -3751,40 +3673,40 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="11">
+      <c r="H81" s="9">
         <f>D81/22</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D82" s="9" t="n">
+      <c r="D82" t="n">
         <v>17</v>
       </c>
-      <c r="E82" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F82" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="10">
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="9">
         <f>D82/22</f>
         <v/>
       </c>
@@ -3817,40 +3739,40 @@
       <c r="G83" t="n">
         <v>1</v>
       </c>
-      <c r="H83" s="11">
+      <c r="H83" s="9">
         <f>D83/22</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D84" s="9" t="n">
+      <c r="D84" t="n">
         <v>16</v>
       </c>
-      <c r="E84" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G84" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H84" s="10">
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" s="9">
         <f>D84/22</f>
         <v/>
       </c>
@@ -3883,40 +3805,40 @@
       <c r="G85" t="n">
         <v>2</v>
       </c>
-      <c r="H85" s="11">
+      <c r="H85" s="9">
         <f>D85/22</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D86" s="9" t="n">
+      <c r="D86" t="n">
         <v>18</v>
       </c>
-      <c r="E86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G86" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="10">
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="9">
         <f>D86/22</f>
         <v/>
       </c>
@@ -3949,40 +3871,40 @@
       <c r="G87" t="n">
         <v>1</v>
       </c>
-      <c r="H87" s="11">
+      <c r="H87" s="9">
         <f>D87/22</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D88" s="9" t="n">
+      <c r="D88" t="n">
         <v>20</v>
       </c>
-      <c r="E88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="10">
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="9">
         <f>D88/22</f>
         <v/>
       </c>
@@ -4015,40 +3937,40 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="11">
+      <c r="H89" s="9">
         <f>D89/22</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D90" s="9" t="n">
+      <c r="D90" t="n">
         <v>16</v>
       </c>
-      <c r="E90" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F90" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G90" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="10">
+      <c r="E90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="9">
         <f>D90/22</f>
         <v/>
       </c>
@@ -4081,40 +4003,40 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" s="11">
+      <c r="H91" s="9">
         <f>D91/22</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D92" s="9" t="n">
+      <c r="D92" t="n">
         <v>21</v>
       </c>
-      <c r="E92" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="10">
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="9">
         <f>D92/22</f>
         <v/>
       </c>
@@ -4147,40 +4069,40 @@
       <c r="G93" t="n">
         <v>2</v>
       </c>
-      <c r="H93" s="11">
+      <c r="H93" s="9">
         <f>D93/22</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D94" s="9" t="n">
+      <c r="D94" t="n">
         <v>17</v>
       </c>
-      <c r="E94" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H94" s="10">
+      <c r="E94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" s="9">
         <f>D94/22</f>
         <v/>
       </c>
@@ -4213,40 +4135,40 @@
       <c r="G95" t="n">
         <v>0</v>
       </c>
-      <c r="H95" s="11">
+      <c r="H95" s="9">
         <f>D95/22</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D96" s="9" t="n">
+      <c r="D96" t="n">
         <v>19</v>
       </c>
-      <c r="E96" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="10">
+      <c r="E96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="9">
         <f>D96/22</f>
         <v/>
       </c>
@@ -4279,40 +4201,40 @@
       <c r="G97" t="n">
         <v>1</v>
       </c>
-      <c r="H97" s="11">
+      <c r="H97" s="9">
         <f>D97/22</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C98" s="9" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D98" s="9" t="n">
+      <c r="D98" t="n">
         <v>16</v>
       </c>
-      <c r="E98" s="9" t="n">
+      <c r="E98" t="n">
         <v>4</v>
       </c>
-      <c r="F98" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H98" s="10">
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="9">
         <f>D98/22</f>
         <v/>
       </c>
@@ -4345,40 +4267,40 @@
       <c r="G99" t="n">
         <v>2</v>
       </c>
-      <c r="H99" s="11">
+      <c r="H99" s="9">
         <f>D99/22</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D100" s="9" t="n">
+      <c r="D100" t="n">
         <v>16</v>
       </c>
-      <c r="E100" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G100" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H100" s="10">
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" s="9">
         <f>D100/22</f>
         <v/>
       </c>
@@ -4411,40 +4333,40 @@
       <c r="G101" t="n">
         <v>1</v>
       </c>
-      <c r="H101" s="11">
+      <c r="H101" s="9">
         <f>D101/22</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D102" s="9" t="n">
+      <c r="D102" t="n">
         <v>17</v>
       </c>
-      <c r="E102" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F102" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" s="10">
+      <c r="E102" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="9">
         <f>D102/22</f>
         <v/>
       </c>
@@ -4477,40 +4399,40 @@
       <c r="G103" t="n">
         <v>1</v>
       </c>
-      <c r="H103" s="11">
+      <c r="H103" s="9">
         <f>D103/22</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D104" s="9" t="n">
+      <c r="D104" t="n">
         <v>18</v>
       </c>
-      <c r="E104" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F104" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" s="10">
+      <c r="E104" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="9">
         <f>D104/22</f>
         <v/>
       </c>
@@ -4543,40 +4465,40 @@
       <c r="G105" t="n">
         <v>1</v>
       </c>
-      <c r="H105" s="11">
+      <c r="H105" s="9">
         <f>D105/22</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D106" s="9" t="n">
+      <c r="D106" t="n">
         <v>14</v>
       </c>
-      <c r="E106" s="9" t="n">
+      <c r="E106" t="n">
         <v>4</v>
       </c>
-      <c r="F106" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" s="10">
+      <c r="F106" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="9">
         <f>D106/22</f>
         <v/>
       </c>
@@ -4609,40 +4531,40 @@
       <c r="G107" t="n">
         <v>1</v>
       </c>
-      <c r="H107" s="11">
+      <c r="H107" s="9">
         <f>D107/22</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D108" s="9" t="n">
+      <c r="D108" t="n">
         <v>19</v>
       </c>
-      <c r="E108" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="10">
+      <c r="E108" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="9">
         <f>D108/22</f>
         <v/>
       </c>
@@ -4675,40 +4597,40 @@
       <c r="G109" t="n">
         <v>1</v>
       </c>
-      <c r="H109" s="11">
+      <c r="H109" s="9">
         <f>D109/22</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D110" s="9" t="n">
+      <c r="D110" t="n">
         <v>14</v>
       </c>
-      <c r="E110" s="9" t="n">
+      <c r="E110" t="n">
         <v>4</v>
       </c>
-      <c r="F110" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G110" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H110" s="10">
+      <c r="F110" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" s="9">
         <f>D110/22</f>
         <v/>
       </c>
@@ -4741,40 +4663,40 @@
       <c r="G111" t="n">
         <v>2</v>
       </c>
-      <c r="H111" s="11">
+      <c r="H111" s="9">
         <f>D111/22</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Ana Marinescu</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D112" s="9" t="n">
+      <c r="D112" t="n">
         <v>19</v>
       </c>
-      <c r="E112" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H112" s="10">
+      <c r="E112" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="9">
         <f>D112/22</f>
         <v/>
       </c>
@@ -4807,40 +4729,40 @@
       <c r="G113" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="11">
+      <c r="H113" s="9">
         <f>D113/22</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>Carmen Popa</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D114" s="9" t="n">
+      <c r="D114" t="n">
         <v>20</v>
       </c>
-      <c r="E114" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="10">
+      <c r="E114" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="9">
         <f>D114/22</f>
         <v/>
       </c>
@@ -4873,40 +4795,40 @@
       <c r="G115" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="11">
+      <c r="H115" s="9">
         <f>D115/22</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Elena Vasile</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D116" s="9" t="n">
+      <c r="D116" t="n">
         <v>19</v>
       </c>
-      <c r="E116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" s="10">
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="9">
         <f>D116/22</f>
         <v/>
       </c>
@@ -4939,40 +4861,40 @@
       <c r="G117" t="n">
         <v>1</v>
       </c>
-      <c r="H117" s="11">
+      <c r="H117" s="9">
         <f>D117/22</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>Georgiana Mara</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D118" s="9" t="n">
+      <c r="D118" t="n">
         <v>20</v>
       </c>
-      <c r="E118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H118" s="10">
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="9">
         <f>D118/22</f>
         <v/>
       </c>
@@ -5005,40 +4927,40 @@
       <c r="G119" t="n">
         <v>2</v>
       </c>
-      <c r="H119" s="11">
+      <c r="H119" s="9">
         <f>D119/22</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B120" s="9" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Ingrid Marinescu</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D120" s="9" t="n">
+      <c r="D120" t="n">
         <v>17</v>
       </c>
-      <c r="E120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G120" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H120" s="10">
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>3</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" s="9">
         <f>D120/22</f>
         <v/>
       </c>
@@ -5071,13 +4993,25 @@
       <c r="G121" t="n">
         <v>1</v>
       </c>
-      <c r="H121" s="11">
+      <c r="H121" s="9">
         <f>D121/22</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H121"/>
+  <conditionalFormatting sqref="H2:H121">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5088,7 +5022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5119,17 +5053,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Total Late Days</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Employee</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Avg Rate</t>
+          <t>Total Late</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5063,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="9">
         <f>AVERAGEIF(Data!$C$2:$C$121,A2,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5148,7 +5072,7 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D2,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5161,15 +5085,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G2,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Ana Marinescu</t>
-        </is>
-      </c>
-      <c r="K2" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J2,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5177,7 +5092,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="9">
         <f>AVERAGEIF(Data!$C$2:$C$121,A3,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5186,7 +5101,7 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D3,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5199,15 +5114,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G3,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Bogdan Radu</t>
-        </is>
-      </c>
-      <c r="K3" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J3,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5215,7 +5121,7 @@
           <t>IT</t>
         </is>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="9">
         <f>AVERAGEIF(Data!$C$2:$C$121,A4,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5224,7 +5130,7 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D4,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5237,15 +5143,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G4,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Carmen Popa</t>
-        </is>
-      </c>
-      <c r="K4" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J4,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5253,7 +5150,7 @@
           <t>Operations</t>
         </is>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="9">
         <f>AVERAGEIF(Data!$C$2:$C$121,A5,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5262,7 +5159,7 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D5,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5275,15 +5172,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G5,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>David Stan</t>
-        </is>
-      </c>
-      <c r="K5" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J5,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5291,7 +5179,7 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <f>AVERAGEIF(Data!$C$2:$C$121,A6,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5300,7 +5188,7 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D6,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5313,15 +5201,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G6,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Elena Vasile</t>
-        </is>
-      </c>
-      <c r="K6" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J6,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="D7" t="inlineStr">
@@ -5329,7 +5208,7 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D7,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5342,15 +5221,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G7,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Filip Barbu</t>
-        </is>
-      </c>
-      <c r="K7" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J7,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="D8" t="inlineStr">
@@ -5358,7 +5228,7 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D8,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5371,15 +5241,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G8,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Georgiana Mara</t>
-        </is>
-      </c>
-      <c r="K8" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J8,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="D9" t="inlineStr">
@@ -5387,7 +5248,7 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D9,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5400,15 +5261,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G9,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Horia Lazarescu</t>
-        </is>
-      </c>
-      <c r="K9" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J9,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="D10" t="inlineStr">
@@ -5416,7 +5268,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D10,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5429,15 +5281,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G10,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Ingrid Marinescu</t>
-        </is>
-      </c>
-      <c r="K10" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J10,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="D11" t="inlineStr">
@@ -5445,7 +5288,7 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D11,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5458,15 +5301,6 @@
         <f>SUMIF(Data!$B$2:$B$121,G11,Data!$E$2:$E$121)</f>
         <v/>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Julian Petrescu</t>
-        </is>
-      </c>
-      <c r="K11" s="11">
-        <f>AVERAGEIF(Data!$B$2:$B$121,J11,Data!$H$2:$H$121)</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="D12" t="inlineStr">
@@ -5474,7 +5308,7 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D12,Data!$H$2:$H$121)</f>
         <v/>
       </c>
@@ -5485,7 +5319,7 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <f>AVERAGEIF(Data!$A$2:$A$121,D13,Data!$H$2:$H$121)</f>
         <v/>
       </c>
